--- a/salidas/cou_bioeconomia_agregado_2022.xlsx
+++ b/salidas/cou_bioeconomia_agregado_2022.xlsx
@@ -10,9 +10,6 @@
   <sheets>
     <sheet name="sut_bioeconomia" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">sut_bioeconomia!$A$1:$W$1</definedName>
-  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -324,24 +321,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -354,7 +355,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -366,7 +367,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFEAF6FB"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -433,10 +449,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -622,2072 +634,2071 @@
   <dimension ref="A1:W34"/>
   <sheetFormatPr defaultColWidth="10.34375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="53.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="2.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="2.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15.59"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="8" style="0" width="14.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="6.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="53.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="2.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="2.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="15.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="8" style="1" width="14.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="4" t="n">
         <v>3284.39505681637</v>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="I2" s="4" t="n">
         <v>146.100487090641</v>
       </c>
-      <c r="J2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" s="3" t="n">
+      <c r="J2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4" t="n">
         <v>1.78368991</v>
       </c>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3" t="n">
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4" t="n">
         <v>504.712739</v>
       </c>
-      <c r="S2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" s="3" t="n">
+      <c r="S2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="4" t="n">
         <v>7.48454643510446</v>
       </c>
-      <c r="U2" s="3" t="n">
+      <c r="U2" s="4" t="n">
         <v>-0.54921898</v>
       </c>
-      <c r="V2" s="3" t="n">
+      <c r="V2" s="4" t="n">
         <v>718.984528658386</v>
       </c>
-      <c r="W2" s="4" t="n">
+      <c r="W2" s="5" t="n">
         <v>4663.9118289305</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="3" t="n">
+      <c r="H3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>5573.17188916911</v>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="J3" s="4" t="n">
         <v>188.274811650098</v>
       </c>
-      <c r="K3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="3" t="n">
+      <c r="K3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4" t="n">
         <v>0.506964658413587</v>
       </c>
-      <c r="N3" s="3" t="n">
+      <c r="N3" s="4" t="n">
         <v>293.345538587945</v>
       </c>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3" t="n">
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4" t="n">
         <v>3216.631535</v>
       </c>
-      <c r="S3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" s="3" t="n">
+      <c r="S3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="4" t="n">
         <v>383.906951504075</v>
       </c>
-      <c r="U3" s="3" t="n">
+      <c r="U3" s="4" t="n">
         <v>-4.6379654</v>
       </c>
-      <c r="V3" s="3" t="n">
+      <c r="V3" s="4" t="n">
         <v>2953.60731924736</v>
       </c>
-      <c r="W3" s="4" t="n">
+      <c r="W3" s="5" t="n">
         <v>12607.807044417</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="3" t="n">
+      <c r="H4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4" t="n">
         <v>0.00262660373172403</v>
       </c>
-      <c r="J4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="3" t="n">
+      <c r="J4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="4" t="n">
         <v>36.3020783441648</v>
       </c>
-      <c r="L4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="3" t="n">
+      <c r="L4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4" t="n">
         <v>2.4010316067682</v>
       </c>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="3" t="n">
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="4" t="n">
         <v>1.67041021720702</v>
       </c>
-      <c r="U4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" s="4" t="n">
+      <c r="U4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" s="5" t="n">
         <v>47.3761467718717</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="3" t="n">
+      <c r="H5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4" t="n">
         <v>30.0342050454556</v>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="J5" s="4" t="n">
         <v>556.915514729602</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="4" t="n">
         <v>0.333787218514663</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="L5" s="4" t="n">
         <v>0.000927939040312919</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" s="4" t="n">
         <v>57.5001324559998</v>
       </c>
-      <c r="N5" s="3" t="n">
+      <c r="N5" s="4" t="n">
         <v>30.7228466826895</v>
       </c>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3" t="n">
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4" t="n">
         <v>8232.274693</v>
       </c>
-      <c r="S5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="3" t="n">
+      <c r="S5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="4" t="n">
         <v>293.886049890507</v>
       </c>
-      <c r="U5" s="3" t="n">
+      <c r="U5" s="4" t="n">
         <v>-0.0040656</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="V5" s="4" t="n">
         <v>7560.98717185339</v>
       </c>
-      <c r="W5" s="4" t="n">
+      <c r="W5" s="5" t="n">
         <v>16765.6512632152</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3" t="n">
+      <c r="H6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4" t="n">
         <v>0.11862231313776</v>
       </c>
-      <c r="J6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="3" t="n">
+      <c r="J6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4" t="n">
         <v>88.1776832759127</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="3" t="n">
+      <c r="M6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4" t="n">
         <v>2170.95998891093</v>
       </c>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3" t="n">
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4" t="n">
         <v>2.86085018</v>
       </c>
-      <c r="S6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="3" t="n">
+      <c r="S6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="4" t="n">
         <v>-85.5985</v>
       </c>
-      <c r="V6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" s="4" t="n">
+      <c r="V6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="5" t="n">
         <v>2182.51864467998</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="3" t="n">
+      <c r="H7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4" t="n">
         <v>3.7058621671639</v>
       </c>
-      <c r="J7" s="3" t="n">
+      <c r="J7" s="4" t="n">
         <v>0.008003964136055</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="4" t="n">
         <v>2469.22710525744</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="L7" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="4" t="n">
         <v>0.00687194388389477</v>
       </c>
-      <c r="N7" s="3" t="n">
+      <c r="N7" s="4" t="n">
         <v>248.897974791649</v>
       </c>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3" t="n">
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4" t="n">
         <v>43.44195667</v>
       </c>
-      <c r="S7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="3" t="n">
+      <c r="S7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="4" t="n">
         <v>17.5591424997775</v>
       </c>
-      <c r="U7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="n">
+      <c r="U7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="4" t="n">
         <v>4.78195261166547E-012</v>
       </c>
-      <c r="W7" s="4" t="n">
+      <c r="W7" s="5" t="n">
         <v>2849.84691729406</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3" t="n">
+      <c r="H8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4" t="n">
         <v>3867.72885253434</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="4" t="n">
         <v>7.54216351344904</v>
       </c>
-      <c r="N8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3" t="n">
+      <c r="N8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4" t="n">
         <v>235.199408</v>
       </c>
-      <c r="S8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="3" t="n">
+      <c r="S8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="4" t="n">
         <v>41.4661716110198</v>
       </c>
-      <c r="U8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="n">
+      <c r="U8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="4" t="n">
         <v>243.409132122258</v>
       </c>
-      <c r="W8" s="4" t="n">
+      <c r="W8" s="5" t="n">
         <v>4397.34572778107</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3" t="n">
+      <c r="H9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4" t="n">
         <v>0.921182626667055</v>
       </c>
-      <c r="J9" s="3" t="n">
+      <c r="J9" s="4" t="n">
         <v>97.2800086016034</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="4" t="n">
         <v>0.0118228591923708</v>
       </c>
-      <c r="L9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="3" t="n">
+      <c r="L9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="4" t="n">
         <v>2195.55243770199</v>
       </c>
-      <c r="N9" s="3" t="n">
+      <c r="N9" s="4" t="n">
         <v>5.75528559402859</v>
       </c>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3" t="n">
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4" t="n">
         <v>18905.7313061993</v>
       </c>
-      <c r="S9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="3" t="n">
+      <c r="S9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="4" t="n">
         <v>1115.23086955679</v>
       </c>
-      <c r="U9" s="3" t="n">
+      <c r="U9" s="4" t="n">
         <v>-115.463719</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="V9" s="4" t="n">
         <v>8622.65433863144</v>
       </c>
-      <c r="W9" s="4" t="n">
+      <c r="W9" s="5" t="n">
         <v>30830.673532771</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="3" t="n">
+      <c r="H10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="4" t="n">
         <v>19670.8148355325</v>
       </c>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="3" t="n">
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="4" t="n">
         <v>16.7337694944648</v>
       </c>
-      <c r="U10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" s="4" t="n">
+      <c r="U10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="5" t="n">
         <v>19692.548605027</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="H11" s="4" t="n">
         <v>0.00380902106930674</v>
       </c>
-      <c r="I11" s="3" t="n">
+      <c r="I11" s="4" t="n">
         <v>117.972158267767</v>
       </c>
-      <c r="J11" s="3" t="n">
+      <c r="J11" s="4" t="n">
         <v>6.64656346388417</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="4" t="n">
         <v>1.84659254654511</v>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="L11" s="4" t="n">
         <v>0.0603270985307416</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="M11" s="4" t="n">
         <v>133.101140687967</v>
       </c>
-      <c r="N11" s="3" t="n">
+      <c r="N11" s="4" t="n">
         <v>19840.0118994313</v>
       </c>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="3" t="n">
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="4" t="n">
         <v>-20099.6424905171</v>
       </c>
-      <c r="W11" s="4" t="n">
+      <c r="W11" s="5" t="n">
         <v>6.0000000000075</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="H12" s="4" t="n">
         <v>2.61742611032783</v>
       </c>
-      <c r="I12" s="3" t="n">
+      <c r="I12" s="4" t="n">
         <v>48.7095260185909</v>
       </c>
-      <c r="J12" s="3" t="n">
+      <c r="J12" s="4" t="n">
         <v>24.0787881071626</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" s="4" t="n">
         <v>526.607889809717</v>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="L12" s="4" t="n">
         <v>1.30237086471202</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" s="4" t="n">
         <v>353.271456324828</v>
       </c>
-      <c r="N12" s="3" t="n">
+      <c r="N12" s="4" t="n">
         <v>50724.2370027736</v>
       </c>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3" t="n">
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4" t="n">
         <v>4899.57177780844</v>
       </c>
-      <c r="S12" s="3" t="n">
+      <c r="S12" s="4" t="n">
         <v>-2363.09618</v>
       </c>
-      <c r="T12" s="3" t="n">
+      <c r="T12" s="4" t="n">
         <v>670.043835822055</v>
       </c>
-      <c r="U12" s="3" t="n">
+      <c r="U12" s="4" t="n">
         <v>-219.16702435</v>
       </c>
-      <c r="V12" s="3" t="n">
+      <c r="V12" s="4" t="n">
         <v>4.23639756608196E-009</v>
       </c>
-      <c r="W12" s="4" t="n">
+      <c r="W12" s="5" t="n">
         <v>54675.1768692937</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3" t="n">
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4" t="n">
         <v>-2363.09618</v>
       </c>
-      <c r="S13" s="3" t="n">
+      <c r="S13" s="4" t="n">
         <v>2363.09618</v>
       </c>
-      <c r="T13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" s="4" t="n">
+      <c r="T13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3" t="n">
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4" t="n">
         <v>223.22317661</v>
       </c>
-      <c r="S14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" s="4" t="n">
+      <c r="S14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="5" t="n">
         <v>223.22317661</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3" t="n">
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4" t="n">
         <v>858.276197</v>
       </c>
-      <c r="S15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" s="4" t="n">
+      <c r="S15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" s="5" t="n">
         <v>858.276197</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" s="4" t="n">
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" s="4" t="n">
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G18" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H18" s="3" t="n">
+      <c r="H18" s="4" t="n">
         <v>223.229075068084</v>
       </c>
-      <c r="I18" s="3" t="n">
+      <c r="I18" s="4" t="n">
         <v>2333.5748292936</v>
       </c>
-      <c r="J18" s="3" t="n">
+      <c r="J18" s="4" t="n">
         <v>2.48125465873558</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="4" t="n">
         <v>199.000753031929</v>
       </c>
-      <c r="L18" s="3" t="n">
+      <c r="L18" s="4" t="n">
         <v>18.4631848350688</v>
       </c>
-      <c r="M18" s="3" t="n">
+      <c r="M18" s="4" t="n">
         <v>0.397459641781622</v>
       </c>
-      <c r="N18" s="3" t="n">
+      <c r="N18" s="4" t="n">
         <v>119.749211471994</v>
       </c>
-      <c r="O18" s="3" t="n">
+      <c r="O18" s="4" t="n">
         <v>1249.81145740177</v>
       </c>
-      <c r="P18" s="3" t="n">
+      <c r="P18" s="4" t="n">
         <v>251.642370963861</v>
       </c>
-      <c r="Q18" s="3" t="n">
+      <c r="Q18" s="4" t="n">
         <v>264.562232563274</v>
       </c>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
-      <c r="U18" s="3"/>
-      <c r="V18" s="3"/>
-      <c r="W18" s="4" t="n">
+      <c r="R18" s="4"/>
+      <c r="S18" s="4"/>
+      <c r="T18" s="4"/>
+      <c r="U18" s="4"/>
+      <c r="V18" s="4"/>
+      <c r="W18" s="5" t="n">
         <v>4663.9118289301</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="H19" s="4" t="n">
         <v>446.886812132858</v>
       </c>
-      <c r="I19" s="3" t="n">
+      <c r="I19" s="4" t="n">
         <v>679.044896980565</v>
       </c>
-      <c r="J19" s="3" t="n">
+      <c r="J19" s="4" t="n">
         <v>92.0329492122343</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="4" t="n">
         <v>688.05569218207</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="4" t="n">
         <v>58.8368380694569</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="M19" s="4" t="n">
         <v>30.0372582328009</v>
       </c>
-      <c r="N19" s="3" t="n">
+      <c r="N19" s="4" t="n">
         <v>839.383609107555</v>
       </c>
-      <c r="O19" s="3" t="n">
+      <c r="O19" s="4" t="n">
         <v>8171.83061759262</v>
       </c>
-      <c r="P19" s="3" t="n">
+      <c r="P19" s="4" t="n">
         <v>558.302023906843</v>
       </c>
-      <c r="Q19" s="3" t="n">
+      <c r="Q19" s="4" t="n">
         <v>1040.396347</v>
       </c>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="4" t="n">
+      <c r="R19" s="4"/>
+      <c r="S19" s="4"/>
+      <c r="T19" s="4"/>
+      <c r="U19" s="4"/>
+      <c r="V19" s="4"/>
+      <c r="W19" s="5" t="n">
         <v>12607.807044417</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H20" s="3" t="n">
+      <c r="H20" s="4" t="n">
         <v>0.180366993446731</v>
       </c>
-      <c r="I20" s="3" t="n">
+      <c r="I20" s="4" t="n">
         <v>0.0425172855201389</v>
       </c>
-      <c r="J20" s="3" t="n">
+      <c r="J20" s="4" t="n">
         <v>0.0457047351822268</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" s="4" t="n">
         <v>0.042139</v>
       </c>
-      <c r="L20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3" t="n">
+      <c r="L20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="4" t="n">
         <v>0.000756139147403605</v>
       </c>
-      <c r="N20" s="3" t="n">
+      <c r="N20" s="4" t="n">
         <v>1.62795691185954</v>
       </c>
-      <c r="O20" s="3" t="n">
+      <c r="O20" s="4" t="n">
         <v>38.4367057067157</v>
       </c>
-      <c r="P20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3"/>
-      <c r="S20" s="3"/>
-      <c r="T20" s="3"/>
-      <c r="U20" s="3"/>
-      <c r="V20" s="3"/>
-      <c r="W20" s="4" t="n">
+      <c r="P20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="4"/>
+      <c r="S20" s="4"/>
+      <c r="T20" s="4"/>
+      <c r="U20" s="4"/>
+      <c r="V20" s="4"/>
+      <c r="W20" s="5" t="n">
         <v>47.3761467718717</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="3" t="n">
+      <c r="H21" s="4" t="n">
         <v>180.379909037537</v>
       </c>
-      <c r="I21" s="3" t="n">
+      <c r="I21" s="4" t="n">
         <v>41.8407809269992</v>
       </c>
-      <c r="J21" s="3" t="n">
+      <c r="J21" s="4" t="n">
         <v>89.1044702810835</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="4" t="n">
         <v>11.548615899286</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="L21" s="4" t="n">
         <v>4.12175064214052</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" s="4" t="n">
         <v>26.9792625149403</v>
       </c>
-      <c r="N21" s="3" t="n">
+      <c r="N21" s="4" t="n">
         <v>577.773499202242</v>
       </c>
-      <c r="O21" s="3" t="n">
+      <c r="O21" s="4" t="n">
         <v>7769.17620803509</v>
       </c>
-      <c r="P21" s="3" t="n">
+      <c r="P21" s="4" t="n">
         <v>2185.84391867588</v>
       </c>
-      <c r="Q21" s="3" t="n">
+      <c r="Q21" s="4" t="n">
         <v>5875.882848</v>
       </c>
-      <c r="R21" s="3"/>
-      <c r="S21" s="3"/>
-      <c r="T21" s="3"/>
-      <c r="U21" s="3"/>
-      <c r="V21" s="3"/>
-      <c r="W21" s="4" t="n">
+      <c r="R21" s="4"/>
+      <c r="S21" s="4"/>
+      <c r="T21" s="4"/>
+      <c r="U21" s="4"/>
+      <c r="V21" s="4"/>
+      <c r="W21" s="5" t="n">
         <v>16765.6512632152</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="G22" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H22" s="3" t="n">
+      <c r="H22" s="4" t="n">
         <v>19.8999597519236</v>
       </c>
-      <c r="I22" s="3" t="n">
+      <c r="I22" s="4" t="n">
         <v>66.9666782368693</v>
       </c>
-      <c r="J22" s="3" t="n">
+      <c r="J22" s="4" t="n">
         <v>9.67960488941932</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="4" t="n">
         <v>58.4218051977547</v>
       </c>
-      <c r="L22" s="3" t="n">
+      <c r="L22" s="4" t="n">
         <v>11.5563727946871</v>
       </c>
-      <c r="M22" s="3" t="n">
+      <c r="M22" s="4" t="n">
         <v>70.5568117569135</v>
       </c>
-      <c r="N22" s="3" t="n">
+      <c r="N22" s="4" t="n">
         <v>1185.05183680887</v>
       </c>
-      <c r="O22" s="3" t="n">
+      <c r="O22" s="4" t="n">
         <v>751.341384253544</v>
       </c>
-      <c r="P22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3" t="n">
+      <c r="P22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="4" t="n">
         <v>5.04419099</v>
       </c>
-      <c r="R22" s="3"/>
-      <c r="S22" s="3"/>
-      <c r="T22" s="3"/>
-      <c r="U22" s="3"/>
-      <c r="V22" s="3"/>
-      <c r="W22" s="4" t="n">
+      <c r="R22" s="4"/>
+      <c r="S22" s="4"/>
+      <c r="T22" s="4"/>
+      <c r="U22" s="4"/>
+      <c r="V22" s="4"/>
+      <c r="W22" s="5" t="n">
         <v>2182.51864467998</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="G23" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H23" s="3" t="n">
+      <c r="H23" s="4" t="n">
         <v>2.04142296496771</v>
       </c>
-      <c r="I23" s="3" t="n">
+      <c r="I23" s="4" t="n">
         <v>12.3601534513468</v>
       </c>
-      <c r="J23" s="3" t="n">
+      <c r="J23" s="4" t="n">
         <v>1.71655010571855</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="4" t="n">
         <v>7.75375027176244</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="L23" s="4" t="n">
         <v>1.82447865417715</v>
       </c>
-      <c r="M23" s="3" t="n">
+      <c r="M23" s="4" t="n">
         <v>14.7207021006938</v>
       </c>
-      <c r="N23" s="3" t="n">
+      <c r="N23" s="4" t="n">
         <v>667.544987267332</v>
       </c>
-      <c r="O23" s="3" t="n">
+      <c r="O23" s="4" t="n">
         <v>1988.3621654077</v>
       </c>
-      <c r="P23" s="3" t="n">
+      <c r="P23" s="4" t="n">
         <v>125.080353500357</v>
       </c>
-      <c r="Q23" s="3" t="n">
+      <c r="Q23" s="4" t="n">
         <v>21.44235357</v>
       </c>
-      <c r="R23" s="3"/>
-      <c r="S23" s="3"/>
-      <c r="T23" s="3"/>
-      <c r="U23" s="3"/>
-      <c r="V23" s="3"/>
-      <c r="W23" s="4" t="n">
+      <c r="R23" s="4"/>
+      <c r="S23" s="4"/>
+      <c r="T23" s="4"/>
+      <c r="U23" s="4"/>
+      <c r="V23" s="4"/>
+      <c r="W23" s="5" t="n">
         <v>2849.84691729406</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G24" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H24" s="3" t="n">
+      <c r="H24" s="4" t="n">
         <v>3.08946906733518</v>
       </c>
-      <c r="I24" s="3" t="n">
+      <c r="I24" s="4" t="n">
         <v>1.7140619414449</v>
       </c>
-      <c r="J24" s="3" t="n">
+      <c r="J24" s="4" t="n">
         <v>0.0919474633353509</v>
       </c>
-      <c r="K24" s="3" t="n">
+      <c r="K24" s="4" t="n">
         <v>0.00063183</v>
       </c>
-      <c r="L24" s="3" t="n">
+      <c r="L24" s="4" t="n">
         <v>37.4738806355643</v>
       </c>
-      <c r="M24" s="3" t="n">
+      <c r="M24" s="4" t="n">
         <v>179.139278107362</v>
       </c>
-      <c r="N24" s="3" t="n">
+      <c r="N24" s="4" t="n">
         <v>1002.82030803788</v>
       </c>
-      <c r="O24" s="3" t="n">
+      <c r="O24" s="4" t="n">
         <v>17.8217829955858</v>
       </c>
-      <c r="P24" s="3" t="n">
+      <c r="P24" s="4" t="n">
         <v>-0.00444546200000005</v>
       </c>
-      <c r="Q24" s="3" t="n">
+      <c r="Q24" s="4" t="n">
         <v>3153.19881316456</v>
       </c>
-      <c r="R24" s="3"/>
-      <c r="S24" s="3"/>
-      <c r="T24" s="3"/>
-      <c r="U24" s="3"/>
-      <c r="V24" s="3"/>
-      <c r="W24" s="4" t="n">
+      <c r="R24" s="4"/>
+      <c r="S24" s="4"/>
+      <c r="T24" s="4"/>
+      <c r="U24" s="4"/>
+      <c r="V24" s="4"/>
+      <c r="W24" s="5" t="n">
         <v>4397.34572778107</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="G25" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H25" s="3" t="n">
+      <c r="H25" s="4" t="n">
         <v>163.735707880045</v>
       </c>
-      <c r="I25" s="3" t="n">
+      <c r="I25" s="4" t="n">
         <v>228.827682163903</v>
       </c>
-      <c r="J25" s="3" t="n">
+      <c r="J25" s="4" t="n">
         <v>178.409071412031</v>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="K25" s="4" t="n">
         <v>71.4900900963239</v>
       </c>
-      <c r="L25" s="3" t="n">
+      <c r="L25" s="4" t="n">
         <v>527.840099317398</v>
       </c>
-      <c r="M25" s="3" t="n">
+      <c r="M25" s="4" t="n">
         <v>661.305573155925</v>
       </c>
-      <c r="N25" s="3" t="n">
+      <c r="N25" s="4" t="n">
         <v>8085.45672224785</v>
       </c>
-      <c r="O25" s="3" t="n">
+      <c r="O25" s="4" t="n">
         <v>4240.01873097089</v>
       </c>
-      <c r="P25" s="3" t="n">
+      <c r="P25" s="4" t="n">
         <v>5803.92334246047</v>
       </c>
-      <c r="Q25" s="3" t="n">
+      <c r="Q25" s="4" t="n">
         <v>10866.6665130709</v>
       </c>
-      <c r="R25" s="3"/>
-      <c r="S25" s="3"/>
-      <c r="T25" s="3"/>
-      <c r="U25" s="3"/>
-      <c r="V25" s="3"/>
-      <c r="W25" s="4" t="n">
+      <c r="R25" s="4"/>
+      <c r="S25" s="4"/>
+      <c r="T25" s="4"/>
+      <c r="U25" s="4"/>
+      <c r="V25" s="4"/>
+      <c r="W25" s="5" t="n">
         <v>30830.6735327757</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="G26" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H26" s="3" t="n">
+      <c r="H26" s="4" t="n">
         <v>22.8989425662836</v>
       </c>
-      <c r="I26" s="3" t="n">
+      <c r="I26" s="4" t="n">
         <v>30.3926089748508</v>
       </c>
-      <c r="J26" s="3" t="n">
+      <c r="J26" s="4" t="n">
         <v>5.34954852905393</v>
       </c>
-      <c r="K26" s="3" t="n">
+      <c r="K26" s="4" t="n">
         <v>18.6964793918805</v>
       </c>
-      <c r="L26" s="3" t="n">
+      <c r="L26" s="4" t="n">
         <v>13.0614957696121</v>
       </c>
-      <c r="M26" s="3" t="n">
+      <c r="M26" s="4" t="n">
         <v>21.268015939339</v>
       </c>
-      <c r="N26" s="3" t="n">
+      <c r="N26" s="4" t="n">
         <v>1282.58690602738</v>
       </c>
-      <c r="O26" s="3" t="n">
+      <c r="O26" s="4" t="n">
         <v>2.05191772964923</v>
       </c>
-      <c r="P26" s="3" t="n">
+      <c r="P26" s="4" t="n">
         <v>18291.2426900989</v>
       </c>
-      <c r="Q26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="3"/>
-      <c r="S26" s="3"/>
-      <c r="T26" s="3"/>
-      <c r="U26" s="3"/>
-      <c r="V26" s="3"/>
-      <c r="W26" s="4" t="n">
+      <c r="Q26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="4"/>
+      <c r="S26" s="4"/>
+      <c r="T26" s="4"/>
+      <c r="U26" s="4"/>
+      <c r="V26" s="4"/>
+      <c r="W26" s="5" t="n">
         <v>19692.548605027</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="G27" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="3"/>
-      <c r="S27" s="3"/>
-      <c r="T27" s="3"/>
-      <c r="U27" s="3"/>
-      <c r="V27" s="3"/>
-      <c r="W27" s="4" t="n">
+      <c r="H27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="4"/>
+      <c r="S27" s="4"/>
+      <c r="T27" s="4"/>
+      <c r="U27" s="4"/>
+      <c r="V27" s="4"/>
+      <c r="W27" s="5" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="G28" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H28" s="3" t="n">
+      <c r="H28" s="4" t="n">
         <v>232.707937381483</v>
       </c>
-      <c r="I28" s="3" t="n">
+      <c r="I28" s="4" t="n">
         <v>381.812183373871</v>
       </c>
-      <c r="J28" s="3" t="n">
+      <c r="J28" s="4" t="n">
         <v>75.4316655906561</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="4" t="n">
         <v>477.598781080885</v>
       </c>
-      <c r="L28" s="3" t="n">
+      <c r="L28" s="4" t="n">
         <v>544.927428665987</v>
       </c>
-      <c r="M28" s="3" t="n">
+      <c r="M28" s="4" t="n">
         <v>425.656624555492</v>
       </c>
-      <c r="N28" s="3" t="n">
+      <c r="N28" s="4" t="n">
         <v>15229.3550913976</v>
       </c>
-      <c r="O28" s="3" t="n">
+      <c r="O28" s="4" t="n">
         <v>26209.2286806871</v>
       </c>
-      <c r="P28" s="3" t="n">
+      <c r="P28" s="4" t="n">
         <v>205.546438056118</v>
       </c>
-      <c r="Q28" s="3" t="n">
+      <c r="Q28" s="4" t="n">
         <v>10885.9120385347</v>
       </c>
-      <c r="R28" s="3"/>
-      <c r="S28" s="3"/>
-      <c r="T28" s="3"/>
-      <c r="U28" s="3"/>
-      <c r="V28" s="3"/>
-      <c r="W28" s="4" t="n">
+      <c r="R28" s="4"/>
+      <c r="S28" s="4"/>
+      <c r="T28" s="4"/>
+      <c r="U28" s="4"/>
+      <c r="V28" s="4"/>
+      <c r="W28" s="5" t="n">
         <v>54675.1768693239</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3"/>
-      <c r="S29" s="3"/>
-      <c r="T29" s="3"/>
-      <c r="U29" s="3"/>
-      <c r="V29" s="3"/>
-      <c r="W29" s="4" t="n">
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="4"/>
+      <c r="S29" s="4"/>
+      <c r="T29" s="4"/>
+      <c r="U29" s="4"/>
+      <c r="V29" s="4"/>
+      <c r="W29" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="3" t="n">
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="4" t="n">
         <v>223.22317661</v>
       </c>
-      <c r="P30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" s="3"/>
-      <c r="S30" s="3"/>
-      <c r="T30" s="3"/>
-      <c r="U30" s="3"/>
-      <c r="V30" s="3"/>
-      <c r="W30" s="4" t="n">
+      <c r="P30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="4"/>
+      <c r="S30" s="4"/>
+      <c r="T30" s="4"/>
+      <c r="U30" s="4"/>
+      <c r="V30" s="4"/>
+      <c r="W30" s="5" t="n">
         <v>223.22317661</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="3" t="n">
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="4" t="n">
         <v>19.3168712167858</v>
       </c>
-      <c r="O31" s="3" t="n">
+      <c r="O31" s="4" t="n">
         <v>838.959325783344</v>
       </c>
-      <c r="P31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="3"/>
-      <c r="S31" s="3"/>
-      <c r="T31" s="3"/>
-      <c r="U31" s="3"/>
-      <c r="V31" s="3"/>
-      <c r="W31" s="4" t="n">
+      <c r="P31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="4"/>
+      <c r="S31" s="4"/>
+      <c r="T31" s="4"/>
+      <c r="U31" s="4"/>
+      <c r="V31" s="4"/>
+      <c r="W31" s="5" t="n">
         <v>858.27619700013</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3" t="n">
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="4" t="n">
         <v>-40.0199999999999</v>
       </c>
-      <c r="P32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3" t="n">
+      <c r="P32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="4" t="n">
         <v>40.02</v>
       </c>
-      <c r="R32" s="3"/>
-      <c r="S32" s="3"/>
-      <c r="T32" s="3"/>
-      <c r="U32" s="3"/>
-      <c r="V32" s="3"/>
-      <c r="W32" s="4" t="n">
+      <c r="R32" s="4"/>
+      <c r="S32" s="4"/>
+      <c r="T32" s="4"/>
+      <c r="U32" s="4"/>
+      <c r="V32" s="4"/>
+      <c r="W32" s="5" t="n">
         <v>1.20792265079217E-013</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="3" t="n">
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="4" t="n">
         <v>-4548.98891627244</v>
       </c>
-      <c r="P33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="3" t="n">
+      <c r="P33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="4" t="n">
         <v>4548.98891627241</v>
       </c>
-      <c r="R33" s="3"/>
-      <c r="S33" s="3"/>
-      <c r="T33" s="3"/>
-      <c r="U33" s="3"/>
-      <c r="V33" s="3"/>
-      <c r="W33" s="4" t="n">
+      <c r="R33" s="4"/>
+      <c r="S33" s="4"/>
+      <c r="T33" s="4"/>
+      <c r="U33" s="4"/>
+      <c r="V33" s="4"/>
+      <c r="W33" s="5" t="n">
         <v>-2.45563569478691E-011</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="3" t="n">
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="4" t="n">
         <v>1991.96668910381</v>
       </c>
-      <c r="I34" s="3" t="n">
+      <c r="I34" s="4" t="n">
         <v>2144.16016667329</v>
       </c>
-      <c r="J34" s="3" t="n">
+      <c r="J34" s="4" t="n">
         <v>418.860923639037</v>
       </c>
-      <c r="K34" s="3" t="n">
+      <c r="K34" s="4" t="n">
         <v>1589.8982213296</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="L34" s="4" t="n">
         <v>2712.98694905253</v>
       </c>
-      <c r="M34" s="3" t="n">
+      <c r="M34" s="4" t="n">
         <v>1317.41942514213</v>
       </c>
-      <c r="N34" s="3" t="n">
+      <c r="N34" s="4" t="n">
         <v>63978.2630941242</v>
       </c>
-      <c r="O34" s="3"/>
-      <c r="P34" s="3"/>
-      <c r="Q34" s="3"/>
-      <c r="R34" s="3"/>
-      <c r="S34" s="3"/>
-      <c r="T34" s="3"/>
-      <c r="U34" s="3"/>
-      <c r="V34" s="3"/>
-      <c r="W34" s="4" t="n">
+      <c r="O34" s="4"/>
+      <c r="P34" s="4"/>
+      <c r="Q34" s="4"/>
+      <c r="R34" s="4"/>
+      <c r="S34" s="4"/>
+      <c r="T34" s="4"/>
+      <c r="U34" s="4"/>
+      <c r="V34" s="4"/>
+      <c r="W34" s="5" t="n">
         <v>74153.5554690645</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W1"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2695,6 +2706,5 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>